--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,45 +1327,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110539372</v>
+        <v>135224675</v>
       </c>
       <c r="B8" t="n">
-        <v>97987</v>
+        <v>99723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224364</v>
+        <v>222541</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>V  Vapnö mosse, Hl</t>
+          <t>Vapnö mosse, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372360</v>
+        <v>372350</v>
       </c>
       <c r="R8" t="n">
-        <v>6292992</v>
+        <v>6293104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1400,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,22 +1418,27 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kirsten Malmström</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126634310</v>
+        <v>110539372</v>
       </c>
       <c r="B9" t="n">
         <v>97987</v>
@@ -1451,23 +1464,19 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vapnö mosse, stig, Hl</t>
+          <t>V  Vapnö mosse, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372369</v>
+        <v>372360</v>
       </c>
       <c r="R9" t="n">
-        <v>6293017</v>
+        <v>6292992</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,15 +1524,229 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Kirsten Malmström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126634310</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vapnö mosse, stig, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>372369</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6293017</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Lars Stibe</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Lars Stibe</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135224633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98064</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vapnö mosse, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>372368</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6292986</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikliga mängder</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsvägkant hygge</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80495104</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115135159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104075058</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102135799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110540051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115160472</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135224675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110539372</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126634310</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,8 +1797,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135224633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>135224675</v>
       </c>
       <c r="B8" t="n">
-        <v>99723</v>
+        <v>99770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135224633</v>
       </c>
       <c r="B11" t="n">
-        <v>98064</v>
+        <v>98108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>135224675</v>
       </c>
       <c r="B8" t="n">
-        <v>99770</v>
+        <v>99797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135224633</v>
       </c>
       <c r="B11" t="n">
-        <v>98108</v>
+        <v>98135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1362,45 +1362,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110539372</v>
+        <v>135224675</v>
       </c>
       <c r="B8" t="n">
-        <v>97987</v>
+        <v>99802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224364</v>
+        <v>222541</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>V  Vapnö mosse, Hl</t>
+          <t>Vapnö mosse, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372360</v>
+        <v>372350</v>
       </c>
       <c r="R8" t="n">
-        <v>6292992</v>
+        <v>6293104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,12 +1435,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,27 +1453,32 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kirsten Malmström</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110539372</t>
+          <t>https://artportalen.se/Sighting/135224675</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126634310</v>
+        <v>110539372</v>
       </c>
       <c r="B9" t="n">
         <v>97987</v>
@@ -1491,23 +1504,19 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vapnö mosse, stig, Hl</t>
+          <t>V  Vapnö mosse, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372369</v>
+        <v>372360</v>
       </c>
       <c r="R9" t="n">
-        <v>6293017</v>
+        <v>6292992</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,12 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,18 +1564,242 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Kirsten Malmström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/110539372</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126634310</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vapnö mosse, stig, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>372369</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6293017</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Stibe</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Stibe</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126634310</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135224633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vapnö mosse, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>372368</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6292986</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikliga mängder</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsvägkant hygge</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135224633</t>
         </is>
       </c>
     </row>
@@ -1580,6 +1813,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>135224675</v>
       </c>
       <c r="B8" t="n">
-        <v>99802</v>
+        <v>99804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135224633</v>
       </c>
       <c r="B11" t="n">
-        <v>98140</v>
+        <v>98142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
